--- a/04_DESIGN_TABLES/DesignTable_4501.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_4501.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,16 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>DH@BORE</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2461,7 +2471,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Air-Way s125 only (double-pass 33 rows); pass1 stated ROWS=33, pass2 35; both enumerate 33</t>
+          <t>[BRENNAN-ONLY 2026-10-18] Air-Way s125 only (double-pass 33 rows); pass1 stated ROWS=33, pass2 35; both enumerate 33 -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2472,6 +2482,14 @@
       <c r="O35" t="inlineStr">
         <is>
           <t>4501-32-32-FG</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>1.843</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2481,24 +2499,52 @@
           <t>4501-06-04-FG</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>3/8</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>4501-06-04-FG</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1/4-18 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-06-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-06-04 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-06-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-06-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.297 (DH@BORE) vs threaded-end drill 0.281 (D1@BORE)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2509,6 +2555,14 @@
       <c r="O36" t="inlineStr">
         <is>
           <t>4501-06-04-FG</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2518,24 +2572,52 @@
           <t>4501-06-06-FG</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3/8</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>4501-06-06-FG</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.297 (DH@BORE) vs threaded-end drill 0.406 (D1@BORE)</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2546,6 +2628,14 @@
       <c r="O37" t="inlineStr">
         <is>
           <t>4501-06-06-FG</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2555,24 +2645,52 @@
           <t>4501-08-06-FG</t>
         </is>
       </c>
+      <c r="B38" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>4501-08-06-FG</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-08-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-08-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-08-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-08-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.406 (DH@BORE) vs threaded-end drill 0.406 (D1@BORE)</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2583,6 +2701,14 @@
       <c r="O38" t="inlineStr">
         <is>
           <t>4501-08-06-FG</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2592,24 +2718,52 @@
           <t>4501-08-08-FG</t>
         </is>
       </c>
+      <c r="B39" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>4501-08-08-FG</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1/2-14 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-08-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.406 (DH@BORE) vs threaded-end drill 0.531 (D1@BORE)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2620,6 +2774,14 @@
       <c r="O39" t="inlineStr">
         <is>
           <t>4501-08-08-FG</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2629,24 +2791,52 @@
           <t>4501-08-12-FG</t>
         </is>
       </c>
+      <c r="B40" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.594</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>4501-08-12-FG</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-08-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-08-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-08-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-08-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.406 (DH@BORE) vs threaded-end drill 0.719 (D1@BORE)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2657,6 +2847,14 @@
       <c r="O40" t="inlineStr">
         <is>
           <t>4501-08-12-FG</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2666,24 +2864,52 @@
           <t>4501-10-08-FG</t>
         </is>
       </c>
+      <c r="B41" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>4501-10-08-FG</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1/2-14 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-10-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-10-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-10-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-10-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.5 (DH@BORE) vs threaded-end drill 0.531 (D1@BORE)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2694,6 +2920,14 @@
       <c r="O41" t="inlineStr">
         <is>
           <t>4501-10-08-FG</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2703,24 +2937,52 @@
           <t>4501-12-08-FG</t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>4501-12-08-FG</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1/2-14 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-12-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-12-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-12-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-12-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.626 (DH@BORE) vs threaded-end drill 0.531 (D1@BORE)</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2731,6 +2993,14 @@
       <c r="O42" t="inlineStr">
         <is>
           <t>4501-12-08-FG</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2740,24 +3010,52 @@
           <t>4501-12-12-FG</t>
         </is>
       </c>
+      <c r="B43" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.595</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>4501-12-12-FG</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.626 (DH@BORE) vs threaded-end drill 0.719 (D1@BORE)</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2768,6 +3066,14 @@
       <c r="O43" t="inlineStr">
         <is>
           <t>4501-12-12-FG</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2777,24 +3083,52 @@
           <t>4501-16-12-FG</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>4501-16-12-FG</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-16-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-16-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-16-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-16-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.843 (DH@BORE) vs threaded-end drill 0.719 (D1@BORE)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -2805,6 +3139,14 @@
       <c r="O44" t="inlineStr">
         <is>
           <t>4501-16-12-FG</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2814,24 +3156,52 @@
           <t>4501-16-16-FG</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>4501-16-16-FG</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1-11 1/2 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-16-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.843 (DH@BORE) vs threaded-end drill 0.938 (D1@BORE)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -2842,6 +3212,14 @@
       <c r="O45" t="inlineStr">
         <is>
           <t>4501-16-16-FG</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2851,24 +3229,52 @@
           <t>4501-20-20-FG</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>4501-20-20-FG</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-20-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4501-20-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4501-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 1.094 (DH@BORE) vs threaded-end drill 1.25 (D1@BORE)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -2879,6 +3285,14 @@
       <c r="O46" t="inlineStr">
         <is>
           <t>4501-20-20-FG</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
